--- a/TestCases.xlsx
+++ b/TestCases.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="3610" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -21,151 +25,214 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
-  <si>
-    <t xml:space="preserve">Test Case ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Function</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Data Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">humanize.number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intcomma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Format integer with thousands separators</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/data/test_data.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Areesha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,234,567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Convert large integer to readable words</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2 million</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ordinal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Convert integer to ordinal string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22nd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">humanize.filesize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">naturalsize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Convert byte count to readable file size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0 MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0 kB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Execution Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total test cases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Failed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test data is read from tests/data/test_data.csv by tests/test_csv_driven.py (pytest.mark.parametrize + csv module).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Result is the value returned by humanize when the test was run (humanize 4.x). Status is calculated from Expected vs Actual.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="66">
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Test Data Source</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>TC-01</t>
+  </si>
+  <si>
+    <t>humanize.number</t>
+  </si>
+  <si>
+    <t>intcomma</t>
+  </si>
+  <si>
+    <t>Format integer with thousands separators</t>
+  </si>
+  <si>
+    <t>1,000</t>
+  </si>
+  <si>
+    <t>tests/data/test_data.csv</t>
+  </si>
+  <si>
+    <t>Areesha</t>
+  </si>
+  <si>
+    <t>TC-02</t>
+  </si>
+  <si>
+    <t>1,234,567</t>
+  </si>
+  <si>
+    <t>TC-03</t>
+  </si>
+  <si>
+    <t>-1,000</t>
+  </si>
+  <si>
+    <t>TC-04</t>
+  </si>
+  <si>
+    <t>intword</t>
+  </si>
+  <si>
+    <t>Convert large integer to readable words</t>
+  </si>
+  <si>
+    <t>1.2 million</t>
+  </si>
+  <si>
+    <t>TC-05</t>
+  </si>
+  <si>
+    <t>ordinal</t>
+  </si>
+  <si>
+    <t>Convert integer to ordinal string</t>
+  </si>
+  <si>
+    <t>22nd</t>
+  </si>
+  <si>
+    <t>TC-06</t>
+  </si>
+  <si>
+    <t>humanize.filesize</t>
+  </si>
+  <si>
+    <t>naturalsize</t>
+  </si>
+  <si>
+    <t>Convert byte count to readable file size</t>
+  </si>
+  <si>
+    <t>1.0 MB</t>
+  </si>
+  <si>
+    <t>TC-07</t>
+  </si>
+  <si>
+    <t>1.0 kB</t>
+  </si>
+  <si>
+    <t>Test Execution Summary</t>
+  </si>
+  <si>
+    <t>Total test cases</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Pass rate</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Test data is read from tests/data/test_data.csv by tests/test_csv_driven.py (pytest.mark.parametrize + csv module).</t>
+  </si>
+  <si>
+    <t>Actual Result is the value returned by humanize when the test was run (humanize 4.x). Status is calculated from Expected vs Actual.</t>
+  </si>
+  <si>
+    <t>humanize.time</t>
+  </si>
+  <si>
+    <t>naturaldelta</t>
+  </si>
+  <si>
+    <t>TC-08</t>
+  </si>
+  <si>
+    <t>Convert timedelta to readable duration</t>
+  </si>
+  <si>
+    <t>timedelta(hours=2)</t>
+  </si>
+  <si>
+    <t>2 hours</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>tests/module_time/test_time_areeba.py</t>
+  </si>
+  <si>
+    <t>Areeba</t>
+  </si>
+  <si>
+    <t>a minute</t>
+  </si>
+  <si>
+    <t>timedelta(seconds=60)</t>
+  </si>
+  <si>
+    <t>Boundary: exactly 60 seconds</t>
+  </si>
+  <si>
+    <t>TC-09</t>
+  </si>
+  <si>
+    <t>TC-10</t>
+  </si>
+  <si>
+    <t>naturaltime</t>
+  </si>
+  <si>
+    <t>Past time shown as “ago”</t>
+  </si>
+  <si>
+    <t>timedelta(seconds=30)</t>
+  </si>
+  <si>
+    <t>30 seconds ago</t>
+  </si>
+  <si>
+    <t>tests/module_filesize/test_filesize_areeba.p</t>
+  </si>
+  <si>
+    <t>1.0 GB</t>
+  </si>
+  <si>
+    <t>Convert 1 billion bytes to GB</t>
+  </si>
+  <si>
+    <t>TC-11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0"/>
-    <numFmt numFmtId="166" formatCode="@"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,46 +241,27 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -231,15 +279,15 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="3">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FF999999"/>
       </left>
@@ -254,78 +302,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -384,47 +405,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -432,12 +469,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -466,7 +503,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -487,7 +524,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -538,7 +575,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -556,34 +593,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -628,7 +664,7 @@
       <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="3">
         <v>1000</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -638,7 +674,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="2" t="str">
-        <f aca="false">IF(F2=G2,"Pass","Fail")</f>
+        <f t="shared" ref="H2:H8" si="0">IF(F2=G2,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -648,7 +684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -661,7 +697,7 @@
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="3">
         <v>1234567</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -671,7 +707,7 @@
         <v>18</v>
       </c>
       <c r="H3" s="2" t="str">
-        <f aca="false">IF(F3=G3,"Pass","Fail")</f>
+        <f t="shared" si="0"/>
         <v>Pass</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -681,7 +717,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -694,7 +730,7 @@
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="3">
         <v>-1000</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -704,7 +740,7 @@
         <v>20</v>
       </c>
       <c r="H4" s="2" t="str">
-        <f aca="false">IF(F4=G4,"Pass","Fail")</f>
+        <f t="shared" si="0"/>
         <v>Pass</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -714,7 +750,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -727,7 +763,7 @@
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="3">
         <v>1200000</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -737,7 +773,7 @@
         <v>24</v>
       </c>
       <c r="H5" s="2" t="str">
-        <f aca="false">IF(F5=G5,"Pass","Fail")</f>
+        <f t="shared" si="0"/>
         <v>Pass</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -747,7 +783,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -760,7 +796,7 @@
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="3">
         <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -770,7 +806,7 @@
         <v>28</v>
       </c>
       <c r="H6" s="2" t="str">
-        <f aca="false">IF(F6=G6,"Pass","Fail")</f>
+        <f t="shared" si="0"/>
         <v>Pass</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -780,7 +816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -793,7 +829,7 @@
       <c r="D7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="3">
         <v>1000000</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -803,7 +839,7 @@
         <v>33</v>
       </c>
       <c r="H7" s="2" t="str">
-        <f aca="false">IF(F7=G7,"Pass","Fail")</f>
+        <f t="shared" si="0"/>
         <v>Pass</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -813,7 +849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -826,7 +862,7 @@
       <c r="D8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="3">
         <v>1024</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -836,7 +872,7 @@
         <v>35</v>
       </c>
       <c r="H8" s="2" t="str">
-        <f aca="false">IF(F8=G8,"Pass","Fail")</f>
+        <f t="shared" si="0"/>
         <v>Pass</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -846,92 +882,207 @@
         <v>16</v>
       </c>
     </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12">
+        <v>1000000000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="6" t="n">
-        <f aca="false">COUNTA('Test Cases'!A2:A8)</f>
+      <c r="B3" s="6">
+        <f>COUNTA('Test Cases'!A2:A8)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF('Test Cases'!H2:H8,"Pass")</f>
+      <c r="B4" s="6">
+        <f>COUNTIF('Test Cases'!H2:H8,"Pass")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF('Test Cases'!H2:H8,"Fail")</f>
+      <c r="B5" s="6">
+        <f>COUNTIF('Test Cases'!H2:H8,"Fail")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="7" t="n">
-        <f aca="false">IF(B3=0,0,B4/B3)</f>
+      <c r="B6" s="7">
+        <f>IF(B3=0,0,B4/B3)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>